--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run3/epoch_60/per_file_predictions_epoch_60.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run3/epoch_60/per_file_predictions_epoch_60.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
   <si>
     <t>Filename</t>
   </si>
@@ -808,766 +808,778 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9688,0.0051,0.0080,0.0058</t>
-  </si>
-  <si>
-    <t>0.0057,0.0005,0.0014,0.9960</t>
-  </si>
-  <si>
-    <t>0.3333,0.0002,0.0001,0.9091</t>
-  </si>
-  <si>
-    <t>0.0219,0.0011,0.0009,0.9921</t>
-  </si>
-  <si>
-    <t>0.9974,0.0006,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9981,0.0002,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9958,0.0009,0.0008,0.0006</t>
-  </si>
-  <si>
-    <t>0.9972,0.0004,0.0004,0.0006</t>
-  </si>
-  <si>
-    <t>0.9916,0.0044,0.0009,0.0011</t>
-  </si>
-  <si>
-    <t>0.9970,0.0003,0.0001,0.0015</t>
-  </si>
-  <si>
-    <t>0.9938,0.0017,0.0007,0.0012</t>
-  </si>
-  <si>
-    <t>0.9968,0.0007,0.0004,0.0009</t>
-  </si>
-  <si>
-    <t>0.8699,0.0089,0.1698,0.0014</t>
-  </si>
-  <si>
-    <t>0.0924,0.0106,0.9103,0.0155</t>
-  </si>
-  <si>
-    <t>0.1677,0.0010,0.9356,0.0002</t>
-  </si>
-  <si>
-    <t>0.3558,0.0121,0.6993,0.0065</t>
-  </si>
-  <si>
-    <t>0.9426,0.0029,0.0376,0.0033</t>
-  </si>
-  <si>
-    <t>0.0038,0.9900,0.0053,0.0028</t>
-  </si>
-  <si>
-    <t>0.0029,0.9875,0.0025,0.0063</t>
-  </si>
-  <si>
-    <t>0.0345,0.9401,0.0299,0.0083</t>
-  </si>
-  <si>
-    <t>0.0160,0.9727,0.0502,0.0015</t>
-  </si>
-  <si>
-    <t>0.0007,0.9977,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9178,0.0017,0.0939,0.0026</t>
-  </si>
-  <si>
-    <t>0.0100,0.0044,0.9856,0.0043</t>
-  </si>
-  <si>
-    <t>0.0151,0.0002,0.9927,0.0002</t>
-  </si>
-  <si>
-    <t>0.0238,0.0040,0.9691,0.0059</t>
-  </si>
-  <si>
-    <t>0.0110,0.0032,0.9874,0.0023</t>
-  </si>
-  <si>
-    <t>0.4093,0.0014,0.7411,0.0026</t>
-  </si>
-  <si>
-    <t>0.0035,0.0006,0.9971,0.0004</t>
-  </si>
-  <si>
-    <t>0.6165,0.4761,0.0218,0.0039</t>
-  </si>
-  <si>
-    <t>0.3073,0.0891,0.6922,0.0055</t>
-  </si>
-  <si>
-    <t>0.0014,0.0055,0.9984,0.0005</t>
-  </si>
-  <si>
-    <t>0.0277,0.7629,0.2806,0.0004</t>
-  </si>
-  <si>
-    <t>0.9767,0.0081,0.0032,0.0044</t>
-  </si>
-  <si>
-    <t>0.9715,0.0141,0.0061,0.0029</t>
-  </si>
-  <si>
-    <t>0.8754,0.1735,0.0099,0.0013</t>
-  </si>
-  <si>
-    <t>0.0282,0.9399,0.1930,0.0019</t>
-  </si>
-  <si>
-    <t>0.0458,0.1997,0.5058,0.0430</t>
-  </si>
-  <si>
-    <t>0.0274,0.0124,0.9230,0.0386</t>
-  </si>
-  <si>
-    <t>0.3123,0.0151,0.8085,0.0015</t>
-  </si>
-  <si>
-    <t>0.0336,0.0011,0.9238,0.0098</t>
-  </si>
-  <si>
-    <t>0.0071,0.1005,0.9912,0.0011</t>
-  </si>
-  <si>
-    <t>0.0017,0.9911,0.0026,0.0010</t>
-  </si>
-  <si>
-    <t>0.0112,0.0141,0.9721,0.0116</t>
-  </si>
-  <si>
-    <t>0.0164,0.2560,0.0017,0.9461</t>
-  </si>
-  <si>
-    <t>0.0117,0.9525,0.0050,0.0523</t>
-  </si>
-  <si>
-    <t>0.0257,0.9628,0.0068,0.0005</t>
-  </si>
-  <si>
-    <t>0.0078,0.9727,0.2708,0.0042</t>
-  </si>
-  <si>
-    <t>0.0027,0.0836,0.9910,0.0018</t>
-  </si>
-  <si>
-    <t>0.0036,0.5528,0.9788,0.0006</t>
-  </si>
-  <si>
-    <t>0.0992,0.0017,0.9262,0.0031</t>
-  </si>
-  <si>
-    <t>0.0154,0.0013,0.9885,0.0013</t>
-  </si>
-  <si>
-    <t>0.0047,0.0031,0.9918,0.0069</t>
-  </si>
-  <si>
-    <t>0.0099,0.0305,0.9791,0.0016</t>
-  </si>
-  <si>
-    <t>0.9732,0.0183,0.0099,0.0022</t>
-  </si>
-  <si>
-    <t>0.9834,0.0011,0.0020,0.0063</t>
-  </si>
-  <si>
-    <t>0.9961,0.0005,0.0007,0.0008</t>
-  </si>
-  <si>
-    <t>0.0035,0.1227,0.9887,0.0225</t>
-  </si>
-  <si>
-    <t>0.9955,0.0004,0.0004,0.0016</t>
-  </si>
-  <si>
-    <t>0.9985,0.0004,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9905,0.0037,0.0018,0.0012</t>
-  </si>
-  <si>
-    <t>0.0020,0.5001,0.9953,0.0001</t>
-  </si>
-  <si>
-    <t>0.0092,0.0884,0.9867,0.0013</t>
-  </si>
-  <si>
-    <t>0.0005,0.0047,0.9961,0.0039</t>
-  </si>
-  <si>
-    <t>0.0005,0.9229,0.9855,0.0001</t>
-  </si>
-  <si>
-    <t>0.0019,0.0022,0.9973,0.0006</t>
-  </si>
-  <si>
-    <t>0.0184,0.9761,0.0379,0.0003</t>
-  </si>
-  <si>
-    <t>0.0063,0.9889,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9505,0.0029,0.0457,0.0017</t>
-  </si>
-  <si>
-    <t>0.9338,0.0062,0.0632,0.0010</t>
-  </si>
-  <si>
-    <t>0.0042,0.0088,0.9902,0.0098</t>
-  </si>
-  <si>
-    <t>0.0005,0.9664,0.8240,0.0003</t>
-  </si>
-  <si>
-    <t>0.0055,0.8618,0.9382,0.0006</t>
-  </si>
-  <si>
-    <t>0.0002,0.9972,0.0043,0.0010</t>
-  </si>
-  <si>
-    <t>0.0021,0.9266,0.8861,0.0023</t>
-  </si>
-  <si>
-    <t>0.0007,0.0001,0.0041,0.9982</t>
-  </si>
-  <si>
-    <t>0.0013,0.0007,0.0002,0.9991</t>
-  </si>
-  <si>
-    <t>0.0042,0.0001,0.0001,0.9984</t>
-  </si>
-  <si>
-    <t>0.0052,0.0009,0.0002,0.9975</t>
-  </si>
-  <si>
-    <t>0.0031,0.0003,0.0045,0.9954</t>
-  </si>
-  <si>
-    <t>0.0096,0.0023,0.0010,0.9939</t>
-  </si>
-  <si>
-    <t>0.0011,0.9312,0.9599,0.0002</t>
-  </si>
-  <si>
-    <t>0.0022,0.8966,0.9705,0.0004</t>
-  </si>
-  <si>
-    <t>0.0098,0.8888,0.1998,0.0078</t>
-  </si>
-  <si>
-    <t>0.0043,0.8725,0.8829,0.0007</t>
-  </si>
-  <si>
-    <t>0.0019,0.9755,0.7800,0.0005</t>
-  </si>
-  <si>
-    <t>0.0069,0.6975,0.7948,0.0047</t>
-  </si>
-  <si>
-    <t>0.9982,0.0003,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9967,0.0008,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.9868,0.0101,0.0026,0.0006</t>
-  </si>
-  <si>
-    <t>0.9932,0.0015,0.0006,0.0017</t>
-  </si>
-  <si>
-    <t>0.9973,0.0003,0.0001,0.0010</t>
-  </si>
-  <si>
-    <t>0.9972,0.0007,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.9900,0.0031,0.0007,0.0033</t>
-  </si>
-  <si>
-    <t>0.9946,0.0034,0.0014,0.0003</t>
-  </si>
-  <si>
-    <t>0.9978,0.0002,0.0002,0.0007</t>
-  </si>
-  <si>
-    <t>0.9977,0.0002,0.0001,0.0010</t>
-  </si>
-  <si>
-    <t>0.9985,0.0001,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9985,0.0002,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9985,0.0001,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9968,0.0002,0.0002,0.0013</t>
-  </si>
-  <si>
-    <t>0.9964,0.0003,0.0005,0.0008</t>
-  </si>
-  <si>
-    <t>0.0062,0.0003,0.9964,0.0003</t>
-  </si>
-  <si>
-    <t>0.0022,0.0030,0.9961,0.0013</t>
-  </si>
-  <si>
-    <t>0.9430,0.0008,0.0080,0.0173</t>
-  </si>
-  <si>
-    <t>0.0041,0.0006,0.9972,0.0002</t>
-  </si>
-  <si>
-    <t>0.0025,0.9933,0.0006,0.0008</t>
-  </si>
-  <si>
-    <t>0.0023,0.9933,0.0032,0.0021</t>
-  </si>
-  <si>
-    <t>0.0212,0.9712,0.0071,0.0008</t>
-  </si>
-  <si>
-    <t>0.0113,0.9794,0.0128,0.0013</t>
-  </si>
-  <si>
-    <t>0.0030,0.9935,0.0035,0.0007</t>
-  </si>
-  <si>
-    <t>0.0025,0.9929,0.0016,0.0008</t>
-  </si>
-  <si>
-    <t>0.6399,0.4933,0.0025,0.0006</t>
-  </si>
-  <si>
-    <t>0.9146,0.0158,0.0604,0.0023</t>
-  </si>
-  <si>
-    <t>0.4799,0.0025,0.6226,0.0048</t>
-  </si>
-  <si>
-    <t>0.4404,0.0214,0.5497,0.0367</t>
-  </si>
-  <si>
-    <t>0.0847,0.0171,0.9182,0.0040</t>
-  </si>
-  <si>
-    <t>0.0176,0.0250,0.0268,0.9730</t>
-  </si>
-  <si>
-    <t>0.0081,0.9882,0.0134,0.0002</t>
-  </si>
-  <si>
-    <t>0.0189,0.9700,0.0210,0.0010</t>
-  </si>
-  <si>
-    <t>0.0036,0.9862,0.0098,0.0104</t>
-  </si>
-  <si>
-    <t>0.0075,0.9597,0.5419,0.0054</t>
-  </si>
-  <si>
-    <t>0.0174,0.9688,0.0249,0.0019</t>
-  </si>
-  <si>
-    <t>0.7524,0.1274,0.1605,0.0058</t>
-  </si>
-  <si>
-    <t>0.8411,0.1210,0.0433,0.0093</t>
-  </si>
-  <si>
-    <t>0.9896,0.0024,0.0038,0.0012</t>
-  </si>
-  <si>
-    <t>0.9864,0.0016,0.0020,0.0055</t>
-  </si>
-  <si>
-    <t>0.9956,0.0003,0.0003,0.0019</t>
-  </si>
-  <si>
-    <t>0.9985,0.0001,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9977,0.0001,0.0002,0.0008</t>
-  </si>
-  <si>
-    <t>0.9952,0.0009,0.0018,0.0004</t>
-  </si>
-  <si>
-    <t>0.9964,0.0007,0.0003,0.0008</t>
-  </si>
-  <si>
-    <t>0.9913,0.0023,0.0024,0.0013</t>
-  </si>
-  <si>
-    <t>0.0039,0.5257,0.8575,0.0102</t>
-  </si>
-  <si>
-    <t>0.0068,0.5529,0.9290,0.0009</t>
-  </si>
-  <si>
-    <t>0.0027,0.0319,0.9848,0.0015</t>
-  </si>
-  <si>
-    <t>0.0293,0.1061,0.9276,0.0060</t>
-  </si>
-  <si>
-    <t>0.8854,0.0037,0.1216,0.0047</t>
-  </si>
-  <si>
-    <t>0.7606,0.0067,0.2477,0.0080</t>
-  </si>
-  <si>
-    <t>0.9740,0.0000,0.0557,0.0000</t>
-  </si>
-  <si>
-    <t>0.2562,0.0167,0.8111,0.0038</t>
-  </si>
-  <si>
-    <t>0.0247,0.0007,0.0006,0.9928</t>
-  </si>
-  <si>
-    <t>0.0000,0.0006,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.0005,0.0008,0.9990</t>
-  </si>
-  <si>
-    <t>0.0024,0.0001,0.0003,0.9987</t>
-  </si>
-  <si>
-    <t>0.0035,0.7459,0.9152,0.0026</t>
-  </si>
-  <si>
-    <t>0.9900,0.0026,0.0004,0.0027</t>
-  </si>
-  <si>
-    <t>0.2527,0.7403,0.0123,0.0283</t>
-  </si>
-  <si>
-    <t>0.9955,0.0003,0.0005,0.0014</t>
-  </si>
-  <si>
-    <t>0.7776,0.2364,0.0133,0.0124</t>
-  </si>
-  <si>
-    <t>0.9959,0.0005,0.0010,0.0002</t>
-  </si>
-  <si>
-    <t>0.2863,0.0212,0.0231,0.8168</t>
-  </si>
-  <si>
-    <t>0.9963,0.0009,0.0007,0.0004</t>
-  </si>
-  <si>
-    <t>0.0017,0.0965,0.9728,0.0344</t>
-  </si>
-  <si>
-    <t>0.9293,0.0021,0.0072,0.0553</t>
-  </si>
-  <si>
-    <t>0.9720,0.0024,0.0113,0.0067</t>
-  </si>
-  <si>
-    <t>0.1043,0.8504,0.0324,0.0200</t>
-  </si>
-  <si>
-    <t>0.9798,0.0018,0.0078,0.0015</t>
-  </si>
-  <si>
-    <t>0.9769,0.0075,0.0082,0.0016</t>
-  </si>
-  <si>
-    <t>0.4872,0.4097,0.0704,0.0647</t>
-  </si>
-  <si>
-    <t>0.8060,0.0480,0.1739,0.0077</t>
-  </si>
-  <si>
-    <t>0.9577,0.0279,0.0114,0.0020</t>
-  </si>
-  <si>
-    <t>0.9718,0.0073,0.0066,0.0099</t>
-  </si>
-  <si>
-    <t>0.9917,0.0015,0.0005,0.0033</t>
-  </si>
-  <si>
-    <t>0.9969,0.0003,0.0005,0.0005</t>
-  </si>
-  <si>
-    <t>0.9965,0.0003,0.0001,0.0013</t>
-  </si>
-  <si>
-    <t>0.9953,0.0009,0.0008,0.0005</t>
-  </si>
-  <si>
-    <t>0.9898,0.0020,0.0012,0.0036</t>
-  </si>
-  <si>
-    <t>0.9959,0.0005,0.0006,0.0011</t>
-  </si>
-  <si>
-    <t>0.9949,0.0002,0.0001,0.0036</t>
-  </si>
-  <si>
-    <t>0.9495,0.0719,0.0014,0.0012</t>
-  </si>
-  <si>
-    <t>0.8805,0.1189,0.0121,0.0022</t>
-  </si>
-  <si>
-    <t>0.3645,0.6904,0.0125,0.0021</t>
-  </si>
-  <si>
-    <t>0.8256,0.0979,0.1259,0.0078</t>
-  </si>
-  <si>
-    <t>0.9816,0.0084,0.0035,0.0029</t>
-  </si>
-  <si>
-    <t>0.9887,0.0049,0.0012,0.0021</t>
-  </si>
-  <si>
-    <t>0.9944,0.0023,0.0010,0.0004</t>
-  </si>
-  <si>
-    <t>0.9824,0.0098,0.0034,0.0015</t>
-  </si>
-  <si>
-    <t>0.0004,0.0122,0.9991,0.0012</t>
-  </si>
-  <si>
-    <t>0.9702,0.0250,0.0054,0.0036</t>
-  </si>
-  <si>
-    <t>0.0026,0.0007,0.9965,0.0006</t>
-  </si>
-  <si>
-    <t>0.0008,0.0052,0.9971,0.0014</t>
-  </si>
-  <si>
-    <t>0.0199,0.0015,0.9874,0.0013</t>
-  </si>
-  <si>
-    <t>0.0104,0.0305,0.9852,0.0009</t>
-  </si>
-  <si>
-    <t>0.0028,0.0031,0.9936,0.0019</t>
-  </si>
-  <si>
-    <t>0.0032,0.0001,0.9973,0.0004</t>
-  </si>
-  <si>
-    <t>0.0073,0.0080,0.9897,0.0026</t>
-  </si>
-  <si>
-    <t>0.3538,0.0018,0.7760,0.0010</t>
-  </si>
-  <si>
-    <t>0.0629,0.0216,0.9252,0.0075</t>
-  </si>
-  <si>
-    <t>0.9546,0.0058,0.0277,0.0006</t>
-  </si>
-  <si>
-    <t>0.2958,0.0601,0.6509,0.0026</t>
-  </si>
-  <si>
-    <t>0.1080,0.1290,0.7601,0.0065</t>
-  </si>
-  <si>
-    <t>0.8126,0.0234,0.1666,0.0023</t>
-  </si>
-  <si>
-    <t>0.7044,0.0081,0.3546,0.0065</t>
-  </si>
-  <si>
-    <t>0.8011,0.0024,0.3356,0.0008</t>
-  </si>
-  <si>
-    <t>0.4839,0.6285,0.0021,0.0019</t>
-  </si>
-  <si>
-    <t>0.7168,0.4126,0.0042,0.0012</t>
-  </si>
-  <si>
-    <t>0.9876,0.0147,0.0007,0.0008</t>
-  </si>
-  <si>
-    <t>0.9868,0.0053,0.0011,0.0037</t>
-  </si>
-  <si>
-    <t>0.7827,0.2662,0.0105,0.0060</t>
-  </si>
-  <si>
-    <t>0.9815,0.0046,0.0061,0.0003</t>
-  </si>
-  <si>
-    <t>0.9851,0.0002,0.0110,0.0002</t>
-  </si>
-  <si>
-    <t>0.9139,0.0029,0.0125,0.0341</t>
-  </si>
-  <si>
-    <t>0.8076,0.0027,0.2960,0.0014</t>
-  </si>
-  <si>
-    <t>0.8452,0.0018,0.1638,0.0037</t>
-  </si>
-  <si>
-    <t>0.0137,0.0013,0.9832,0.0145</t>
-  </si>
-  <si>
-    <t>0.0301,0.0674,0.8979,0.0269</t>
-  </si>
-  <si>
-    <t>0.0864,0.0124,0.9169,0.0042</t>
-  </si>
-  <si>
-    <t>0.0392,0.0029,0.9715,0.0010</t>
-  </si>
-  <si>
-    <t>0.0096,0.9369,0.0485,0.0136</t>
-  </si>
-  <si>
-    <t>0.9937,0.0003,0.0002,0.0049</t>
-  </si>
-  <si>
-    <t>0.9958,0.0007,0.0004,0.0011</t>
-  </si>
-  <si>
-    <t>0.9932,0.0024,0.0006,0.0021</t>
-  </si>
-  <si>
-    <t>0.9966,0.0018,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9912,0.0031,0.0016,0.0018</t>
-  </si>
-  <si>
-    <t>0.9968,0.0006,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.9974,0.0001,0.0001,0.0012</t>
-  </si>
-  <si>
-    <t>0.9972,0.0005,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.0052,0.0399,0.9878,0.0060</t>
-  </si>
-  <si>
-    <t>0.2348,0.1208,0.7314,0.0091</t>
-  </si>
-  <si>
-    <t>0.9358,0.0025,0.0272,0.0113</t>
-  </si>
-  <si>
-    <t>0.0482,0.0020,0.9703,0.0003</t>
-  </si>
-  <si>
-    <t>0.0003,0.0007,0.9917,0.0229</t>
-  </si>
-  <si>
-    <t>0.0100,0.0104,0.9833,0.0008</t>
-  </si>
-  <si>
-    <t>0.0009,0.0019,0.9987,0.0005</t>
-  </si>
-  <si>
-    <t>0.0164,0.0017,0.9880,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.0007,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0094,0.0120,0.9726,0.0022</t>
-  </si>
-  <si>
-    <t>0.2484,0.0107,0.7993,0.0175</t>
-  </si>
-  <si>
-    <t>0.9456,0.0008,0.0491,0.0015</t>
-  </si>
-  <si>
-    <t>0.9019,0.0005,0.1436,0.0008</t>
-  </si>
-  <si>
-    <t>0.9956,0.0002,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.9870,0.0054,0.0036,0.0022</t>
-  </si>
-  <si>
-    <t>0.9902,0.0019,0.0011,0.0024</t>
-  </si>
-  <si>
-    <t>0.9977,0.0005,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9881,0.0103,0.0005,0.0011</t>
-  </si>
-  <si>
-    <t>0.9979,0.0001,0.0001,0.0008</t>
-  </si>
-  <si>
-    <t>0.9917,0.0016,0.0015,0.0018</t>
-  </si>
-  <si>
-    <t>0.9959,0.0012,0.0004,0.0008</t>
-  </si>
-  <si>
-    <t>0.9946,0.0010,0.0002,0.0025</t>
-  </si>
-  <si>
-    <t>0.0040,0.2114,0.8684,0.0039</t>
-  </si>
-  <si>
-    <t>0.0090,0.0041,0.9911,0.0004</t>
-  </si>
-  <si>
-    <t>0.0071,0.0214,0.9863,0.0017</t>
-  </si>
-  <si>
-    <t>0.1024,0.0593,0.7851,0.0294</t>
-  </si>
-  <si>
-    <t>0.0028,0.0005,0.9978,0.0001</t>
-  </si>
-  <si>
-    <t>0.4306,0.0020,0.5119,0.0198</t>
-  </si>
-  <si>
-    <t>0.0622,0.0161,0.9256,0.0049</t>
-  </si>
-  <si>
-    <t>0.5288,0.0127,0.4607,0.0265</t>
-  </si>
-  <si>
-    <t>0.9670,0.0012,0.0011,0.0366</t>
-  </si>
-  <si>
-    <t>0.0215,0.0014,0.0026,0.9885</t>
-  </si>
-  <si>
-    <t>0.0058,0.0006,0.0006,0.9962</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0002,0.9998</t>
-  </si>
-  <si>
-    <t>0.0016,0.0002,0.0004,0.9989</t>
-  </si>
-  <si>
-    <t>0.8309,0.0257,0.0973,0.0639</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.9851,0.0029,0.0008,0.0037</t>
+  </si>
+  <si>
+    <t>0.0061,0.0001,0.0011,0.9953</t>
+  </si>
+  <si>
+    <t>0.8470,0.0009,0.0016,0.2388</t>
+  </si>
+  <si>
+    <t>0.1504,0.0057,0.0029,0.9435</t>
+  </si>
+  <si>
+    <t>0.9978,0.0003,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9963,0.0007,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9928,0.0008,0.0005,0.0033</t>
+  </si>
+  <si>
+    <t>0.9986,0.0002,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9946,0.0035,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9947,0.0016,0.0004,0.0012</t>
+  </si>
+  <si>
+    <t>0.9984,0.0002,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9952,0.0005,0.0002,0.0024</t>
+  </si>
+  <si>
+    <t>0.9876,0.0012,0.0056,0.0002</t>
+  </si>
+  <si>
+    <t>0.2656,0.0023,0.8662,0.0014</t>
+  </si>
+  <si>
+    <t>0.4626,0.0056,0.6622,0.0014</t>
+  </si>
+  <si>
+    <t>0.0568,0.0027,0.9626,0.0011</t>
+  </si>
+  <si>
+    <t>0.8899,0.0043,0.0851,0.0054</t>
+  </si>
+  <si>
+    <t>0.0017,0.9969,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0034,0.9880,0.0019,0.0044</t>
+  </si>
+  <si>
+    <t>0.1300,0.8477,0.0069,0.0056</t>
+  </si>
+  <si>
+    <t>0.0465,0.9534,0.0051,0.0006</t>
+  </si>
+  <si>
+    <t>0.0110,0.9823,0.0029,0.0008</t>
+  </si>
+  <si>
+    <t>0.8431,0.0087,0.1829,0.0075</t>
+  </si>
+  <si>
+    <t>0.7199,0.0064,0.3240,0.0089</t>
+  </si>
+  <si>
+    <t>0.0067,0.0003,0.9952,0.0002</t>
+  </si>
+  <si>
+    <t>0.2854,0.0436,0.7326,0.0129</t>
+  </si>
+  <si>
+    <t>0.0047,0.0025,0.9923,0.0057</t>
+  </si>
+  <si>
+    <t>0.0146,0.0006,0.9719,0.0111</t>
+  </si>
+  <si>
+    <t>0.0065,0.0005,0.9963,0.0002</t>
+  </si>
+  <si>
+    <t>0.2861,0.7209,0.0327,0.0198</t>
+  </si>
+  <si>
+    <t>0.9090,0.0409,0.0446,0.0027</t>
+  </si>
+  <si>
+    <t>0.0024,0.0062,0.9931,0.0145</t>
+  </si>
+  <si>
+    <t>0.0235,0.9357,0.0460,0.0016</t>
+  </si>
+  <si>
+    <t>0.8303,0.0720,0.0940,0.0373</t>
+  </si>
+  <si>
+    <t>0.8561,0.0386,0.0891,0.0065</t>
+  </si>
+  <si>
+    <t>0.5823,0.5220,0.0091,0.0014</t>
+  </si>
+  <si>
+    <t>0.0060,0.9798,0.1624,0.0038</t>
+  </si>
+  <si>
+    <t>0.0082,0.4757,0.1697,0.0862</t>
+  </si>
+  <si>
+    <t>0.0247,0.0019,0.9492,0.0133</t>
+  </si>
+  <si>
+    <t>0.5531,0.0068,0.5031,0.0084</t>
+  </si>
+  <si>
+    <t>0.0255,0.0007,0.9246,0.0304</t>
+  </si>
+  <si>
+    <t>0.0159,0.0324,0.9835,0.0026</t>
+  </si>
+  <si>
+    <t>0.0111,0.9752,0.0047,0.0006</t>
+  </si>
+  <si>
+    <t>0.0143,0.0156,0.9678,0.0115</t>
+  </si>
+  <si>
+    <t>0.0276,0.2655,0.0150,0.9392</t>
+  </si>
+  <si>
+    <t>0.0189,0.9483,0.0117,0.0354</t>
+  </si>
+  <si>
+    <t>0.0098,0.9730,0.0277,0.0018</t>
+  </si>
+  <si>
+    <t>0.0054,0.9836,0.0870,0.0023</t>
+  </si>
+  <si>
+    <t>0.0010,0.0551,0.9896,0.0034</t>
+  </si>
+  <si>
+    <t>0.0078,0.3097,0.9749,0.0008</t>
+  </si>
+  <si>
+    <t>0.0374,0.0025,0.9657,0.0032</t>
+  </si>
+  <si>
+    <t>0.8056,0.0001,0.4440,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.0013,0.9980,0.0020</t>
+  </si>
+  <si>
+    <t>0.0070,0.0427,0.9815,0.0007</t>
+  </si>
+  <si>
+    <t>0.9489,0.0721,0.0043,0.0013</t>
+  </si>
+  <si>
+    <t>0.9768,0.0034,0.0098,0.0030</t>
+  </si>
+  <si>
+    <t>0.9875,0.0012,0.0026,0.0032</t>
+  </si>
+  <si>
+    <t>0.0013,0.0367,0.9957,0.0330</t>
+  </si>
+  <si>
+    <t>0.9959,0.0007,0.0005,0.0008</t>
+  </si>
+  <si>
+    <t>0.9970,0.0014,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9982,0.0005,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.0012,0.3163,0.9974,0.0002</t>
+  </si>
+  <si>
+    <t>0.0311,0.3675,0.8438,0.0056</t>
+  </si>
+  <si>
+    <t>0.0049,0.0024,0.9934,0.0007</t>
+  </si>
+  <si>
+    <t>0.0010,0.6342,0.9908,0.0002</t>
+  </si>
+  <si>
+    <t>0.0043,0.0077,0.9938,0.0015</t>
+  </si>
+  <si>
+    <t>0.0714,0.9287,0.0189,0.0006</t>
+  </si>
+  <si>
+    <t>0.0032,0.9935,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9408,0.0057,0.0638,0.0013</t>
+  </si>
+  <si>
+    <t>0.8752,0.0482,0.0693,0.0068</t>
+  </si>
+  <si>
+    <t>0.0054,0.0142,0.9903,0.0090</t>
+  </si>
+  <si>
+    <t>0.0015,0.8910,0.9519,0.0003</t>
+  </si>
+  <si>
+    <t>0.0016,0.9768,0.5370,0.0004</t>
+  </si>
+  <si>
+    <t>0.0003,0.9972,0.0046,0.0004</t>
+  </si>
+  <si>
+    <t>0.0008,0.9784,0.8508,0.0004</t>
+  </si>
+  <si>
+    <t>0.0032,0.0001,0.0005,0.9983</t>
+  </si>
+  <si>
+    <t>0.0003,0.0005,0.0003,0.9995</t>
+  </si>
+  <si>
+    <t>0.0029,0.0001,0.0003,0.9984</t>
+  </si>
+  <si>
+    <t>0.0025,0.0022,0.0004,0.9980</t>
+  </si>
+  <si>
+    <t>0.0009,0.0002,0.0005,0.9990</t>
+  </si>
+  <si>
+    <t>0.0014,0.0020,0.0022,0.9974</t>
+  </si>
+  <si>
+    <t>0.0037,0.8745,0.9162,0.0007</t>
+  </si>
+  <si>
+    <t>0.0046,0.5356,0.9855,0.0011</t>
+  </si>
+  <si>
+    <t>0.0091,0.6451,0.5822,0.0175</t>
+  </si>
+  <si>
+    <t>0.0050,0.7473,0.8995,0.0009</t>
+  </si>
+  <si>
+    <t>0.0020,0.9538,0.9128,0.0003</t>
+  </si>
+  <si>
+    <t>0.0036,0.9184,0.7282,0.0006</t>
+  </si>
+  <si>
+    <t>0.9927,0.0037,0.0016,0.0006</t>
+  </si>
+  <si>
+    <t>0.9939,0.0021,0.0014,0.0007</t>
+  </si>
+  <si>
+    <t>0.9930,0.0030,0.0004,0.0015</t>
+  </si>
+  <si>
+    <t>0.9943,0.0011,0.0002,0.0019</t>
+  </si>
+  <si>
+    <t>0.9937,0.0013,0.0023,0.0004</t>
+  </si>
+  <si>
+    <t>0.9972,0.0009,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9949,0.0007,0.0004,0.0019</t>
+  </si>
+  <si>
+    <t>0.9952,0.0030,0.0006,0.0005</t>
+  </si>
+  <si>
+    <t>0.9971,0.0003,0.0002,0.0009</t>
+  </si>
+  <si>
+    <t>0.9987,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9977,0.0001,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9976,0.0002,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.9982,0.0003,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9978,0.0003,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.9935,0.0023,0.0008,0.0021</t>
+  </si>
+  <si>
+    <t>0.9973,0.0002,0.0001,0.0012</t>
+  </si>
+  <si>
+    <t>0.0009,0.0004,0.9982,0.0020</t>
+  </si>
+  <si>
+    <t>0.0420,0.0010,0.9841,0.0002</t>
+  </si>
+  <si>
+    <t>0.9378,0.0046,0.0222,0.0088</t>
+  </si>
+  <si>
+    <t>0.0022,0.0002,0.9985,0.0001</t>
+  </si>
+  <si>
+    <t>0.0213,0.9647,0.0045,0.0026</t>
+  </si>
+  <si>
+    <t>0.0068,0.9882,0.0016,0.0003</t>
+  </si>
+  <si>
+    <t>0.0602,0.9139,0.0099,0.0103</t>
+  </si>
+  <si>
+    <t>0.0285,0.9749,0.0026,0.0002</t>
+  </si>
+  <si>
+    <t>0.0075,0.9868,0.0074,0.0007</t>
+  </si>
+  <si>
+    <t>0.0025,0.9938,0.0020,0.0004</t>
+  </si>
+  <si>
+    <t>0.1963,0.8123,0.0047,0.0022</t>
+  </si>
+  <si>
+    <t>0.4535,0.3403,0.2230,0.0394</t>
+  </si>
+  <si>
+    <t>0.4513,0.0033,0.6852,0.0019</t>
+  </si>
+  <si>
+    <t>0.7079,0.1325,0.0979,0.0598</t>
+  </si>
+  <si>
+    <t>0.6427,0.0080,0.4594,0.0030</t>
+  </si>
+  <si>
+    <t>0.0148,0.0410,0.1013,0.9538</t>
+  </si>
+  <si>
+    <t>0.0133,0.9728,0.0657,0.0017</t>
+  </si>
+  <si>
+    <t>0.0036,0.9868,0.0227,0.0026</t>
+  </si>
+  <si>
+    <t>0.0012,0.9934,0.0108,0.0062</t>
+  </si>
+  <si>
+    <t>0.0018,0.9768,0.2965,0.0103</t>
+  </si>
+  <si>
+    <t>0.0522,0.9543,0.0026,0.0003</t>
+  </si>
+  <si>
+    <t>0.6789,0.3060,0.0440,0.0029</t>
+  </si>
+  <si>
+    <t>0.8990,0.0985,0.0132,0.0014</t>
+  </si>
+  <si>
+    <t>0.9939,0.0003,0.0011,0.0011</t>
+  </si>
+  <si>
+    <t>0.9909,0.0002,0.0005,0.0045</t>
+  </si>
+  <si>
+    <t>0.9960,0.0001,0.0001,0.0028</t>
+  </si>
+  <si>
+    <t>0.9956,0.0008,0.0011,0.0005</t>
+  </si>
+  <si>
+    <t>0.9991,0.0000,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9962,0.0007,0.0006,0.0007</t>
+  </si>
+  <si>
+    <t>0.9974,0.0003,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9963,0.0002,0.0003,0.0011</t>
+  </si>
+  <si>
+    <t>0.0028,0.2731,0.9922,0.0002</t>
+  </si>
+  <si>
+    <t>0.0122,0.6628,0.8800,0.0016</t>
+  </si>
+  <si>
+    <t>0.0060,0.0572,0.9684,0.0026</t>
+  </si>
+  <si>
+    <t>0.0049,0.0407,0.9836,0.0003</t>
+  </si>
+  <si>
+    <t>0.9946,0.0010,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.7945,0.0020,0.2710,0.0023</t>
+  </si>
+  <si>
+    <t>0.7962,0.0007,0.3074,0.0015</t>
+  </si>
+  <si>
+    <t>0.8100,0.0147,0.2099,0.0068</t>
+  </si>
+  <si>
+    <t>0.0109,0.0008,0.0004,0.9954</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0002,0.9999</t>
+  </si>
+  <si>
+    <t>0.0006,0.0003,0.0016,0.9988</t>
+  </si>
+  <si>
+    <t>0.0007,0.0001,0.0023,0.9988</t>
+  </si>
+  <si>
+    <t>0.0026,0.8233,0.9389,0.0006</t>
+  </si>
+  <si>
+    <t>0.9974,0.0004,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.1994,0.7804,0.0288,0.0222</t>
+  </si>
+  <si>
+    <t>0.9923,0.0006,0.0008,0.0032</t>
+  </si>
+  <si>
+    <t>0.8147,0.2108,0.0075,0.0086</t>
+  </si>
+  <si>
+    <t>0.9961,0.0001,0.0003,0.0010</t>
+  </si>
+  <si>
+    <t>0.9007,0.0144,0.0087,0.0948</t>
+  </si>
+  <si>
+    <t>0.9962,0.0005,0.0003,0.0010</t>
+  </si>
+  <si>
+    <t>0.0026,0.6611,0.9467,0.0104</t>
+  </si>
+  <si>
+    <t>0.9877,0.0006,0.0010,0.0051</t>
+  </si>
+  <si>
+    <t>0.8576,0.0027,0.0216,0.0913</t>
+  </si>
+  <si>
+    <t>0.0852,0.8727,0.0364,0.0123</t>
+  </si>
+  <si>
+    <t>0.9972,0.0006,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9661,0.0123,0.0091,0.0038</t>
+  </si>
+  <si>
+    <t>0.3396,0.6103,0.0739,0.0283</t>
+  </si>
+  <si>
+    <t>0.9061,0.0253,0.0521,0.0070</t>
+  </si>
+  <si>
+    <t>0.9765,0.0113,0.0053,0.0025</t>
+  </si>
+  <si>
+    <t>0.9903,0.0016,0.0017,0.0030</t>
+  </si>
+  <si>
+    <t>0.9963,0.0004,0.0003,0.0014</t>
+  </si>
+  <si>
+    <t>0.9915,0.0027,0.0022,0.0009</t>
+  </si>
+  <si>
+    <t>0.9973,0.0002,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9936,0.0007,0.0006,0.0020</t>
+  </si>
+  <si>
+    <t>0.9928,0.0012,0.0006,0.0023</t>
+  </si>
+  <si>
+    <t>0.9927,0.0003,0.0004,0.0040</t>
+  </si>
+  <si>
+    <t>0.9936,0.0004,0.0004,0.0027</t>
+  </si>
+  <si>
+    <t>0.9416,0.0601,0.0010,0.0022</t>
+  </si>
+  <si>
+    <t>0.5699,0.5037,0.0081,0.0026</t>
+  </si>
+  <si>
+    <t>0.4362,0.5750,0.0340,0.0053</t>
+  </si>
+  <si>
+    <t>0.9492,0.0065,0.0316,0.0049</t>
+  </si>
+  <si>
+    <t>0.9953,0.0020,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9888,0.0011,0.0018,0.0026</t>
+  </si>
+  <si>
+    <t>0.9807,0.0093,0.0045,0.0026</t>
+  </si>
+  <si>
+    <t>0.9823,0.0066,0.0005,0.0035</t>
+  </si>
+  <si>
+    <t>0.0012,0.0074,0.9986,0.0004</t>
+  </si>
+  <si>
+    <t>0.9904,0.0072,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.0059,0.0007,0.9943,0.0005</t>
+  </si>
+  <si>
+    <t>0.0170,0.0706,0.9702,0.0135</t>
+  </si>
+  <si>
+    <t>0.0882,0.0017,0.9553,0.0019</t>
+  </si>
+  <si>
+    <t>0.0058,0.0141,0.9888,0.0008</t>
+  </si>
+  <si>
+    <t>0.0139,0.0249,0.9688,0.0041</t>
+  </si>
+  <si>
+    <t>0.0148,0.0003,0.9881,0.0016</t>
+  </si>
+  <si>
+    <t>0.0066,0.0062,0.9905,0.0014</t>
+  </si>
+  <si>
+    <t>0.7960,0.0067,0.2258,0.0061</t>
+  </si>
+  <si>
+    <t>0.8197,0.0052,0.2447,0.0026</t>
+  </si>
+  <si>
+    <t>0.5881,0.0217,0.4948,0.0121</t>
+  </si>
+  <si>
+    <t>0.2874,0.1095,0.6916,0.0386</t>
+  </si>
+  <si>
+    <t>0.2156,0.0215,0.7854,0.0039</t>
+  </si>
+  <si>
+    <t>0.7711,0.0028,0.4085,0.0003</t>
+  </si>
+  <si>
+    <t>0.2500,0.0187,0.7477,0.0236</t>
+  </si>
+  <si>
+    <t>0.3650,0.0515,0.6440,0.0075</t>
+  </si>
+  <si>
+    <t>0.5086,0.6643,0.0013,0.0003</t>
+  </si>
+  <si>
+    <t>0.7618,0.3556,0.0029,0.0014</t>
+  </si>
+  <si>
+    <t>0.9832,0.0199,0.0017,0.0009</t>
+  </si>
+  <si>
+    <t>0.9621,0.0370,0.0013,0.0030</t>
+  </si>
+  <si>
+    <t>0.6441,0.4422,0.0015,0.0029</t>
+  </si>
+  <si>
+    <t>0.9713,0.0042,0.0157,0.0002</t>
+  </si>
+  <si>
+    <t>0.9908,0.0002,0.0054,0.0002</t>
+  </si>
+  <si>
+    <t>0.9711,0.0003,0.0041,0.0068</t>
+  </si>
+  <si>
+    <t>0.8770,0.0093,0.1325,0.0033</t>
+  </si>
+  <si>
+    <t>0.3418,0.0014,0.7818,0.0024</t>
+  </si>
+  <si>
+    <t>0.0546,0.0030,0.9430,0.0126</t>
+  </si>
+  <si>
+    <t>0.0092,0.0509,0.9716,0.0052</t>
+  </si>
+  <si>
+    <t>0.0385,0.0140,0.9527,0.0059</t>
+  </si>
+  <si>
+    <t>0.6373,0.0012,0.5211,0.0009</t>
+  </si>
+  <si>
+    <t>0.0453,0.0397,0.9371,0.0028</t>
+  </si>
+  <si>
+    <t>0.9928,0.0014,0.0002,0.0029</t>
+  </si>
+  <si>
+    <t>0.9921,0.0017,0.0017,0.0019</t>
+  </si>
+  <si>
+    <t>0.9928,0.0022,0.0004,0.0022</t>
+  </si>
+  <si>
+    <t>0.9952,0.0013,0.0011,0.0004</t>
+  </si>
+  <si>
+    <t>0.9925,0.0043,0.0011,0.0007</t>
+  </si>
+  <si>
+    <t>0.9901,0.0010,0.0005,0.0054</t>
+  </si>
+  <si>
+    <t>0.9967,0.0004,0.0001,0.0016</t>
+  </si>
+  <si>
+    <t>0.9980,0.0003,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.1330,0.0221,0.9142,0.0023</t>
+  </si>
+  <si>
+    <t>0.1498,0.2253,0.7267,0.0290</t>
+  </si>
+  <si>
+    <t>0.9418,0.0037,0.0369,0.0041</t>
+  </si>
+  <si>
+    <t>0.0051,0.0020,0.9951,0.0004</t>
+  </si>
+  <si>
+    <t>0.0009,0.0010,0.9964,0.0032</t>
+  </si>
+  <si>
+    <t>0.0364,0.1494,0.8656,0.0072</t>
+  </si>
+  <si>
+    <t>0.0012,0.0018,0.9989,0.0002</t>
+  </si>
+  <si>
+    <t>0.0625,0.0067,0.9559,0.0034</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0098,0.0027,0.9889,0.0006</t>
+  </si>
+  <si>
+    <t>0.0610,0.0390,0.9120,0.0033</t>
+  </si>
+  <si>
+    <t>0.9438,0.0003,0.0700,0.0007</t>
+  </si>
+  <si>
+    <t>0.8022,0.0002,0.2646,0.0012</t>
+  </si>
+  <si>
+    <t>0.9852,0.0006,0.0068,0.0007</t>
+  </si>
+  <si>
+    <t>0.9958,0.0002,0.0001,0.0024</t>
+  </si>
+  <si>
+    <t>0.9924,0.0014,0.0014,0.0013</t>
+  </si>
+  <si>
+    <t>0.9957,0.0021,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.9916,0.0053,0.0010,0.0008</t>
+  </si>
+  <si>
+    <t>0.9961,0.0002,0.0002,0.0028</t>
+  </si>
+  <si>
+    <t>0.9972,0.0004,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9956,0.0009,0.0002,0.0012</t>
+  </si>
+  <si>
+    <t>0.9934,0.0023,0.0006,0.0017</t>
+  </si>
+  <si>
+    <t>0.0406,0.0188,0.9396,0.0049</t>
+  </si>
+  <si>
+    <t>0.0207,0.1117,0.9478,0.0011</t>
+  </si>
+  <si>
+    <t>0.0314,0.0227,0.9532,0.0063</t>
+  </si>
+  <si>
+    <t>0.0609,0.0081,0.9464,0.0033</t>
+  </si>
+  <si>
+    <t>0.0034,0.0002,0.9973,0.0001</t>
+  </si>
+  <si>
+    <t>0.1134,0.0006,0.7279,0.0296</t>
+  </si>
+  <si>
+    <t>0.1083,0.0518,0.8421,0.0656</t>
+  </si>
+  <si>
+    <t>0.4084,0.0618,0.2657,0.2283</t>
+  </si>
+  <si>
+    <t>0.9785,0.0009,0.0024,0.0099</t>
+  </si>
+  <si>
+    <t>0.0058,0.0006,0.0005,0.9972</t>
+  </si>
+  <si>
+    <t>0.0149,0.0004,0.0016,0.9884</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.0002,0.9997</t>
+  </si>
+  <si>
+    <t>0.0025,0.0001,0.0001,0.9991</t>
+  </si>
+  <si>
+    <t>0.8019,0.0013,0.0057,0.2611</t>
   </si>
 </sst>
 </file>
@@ -1953,7 +1965,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1967,7 +1979,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1978,10 +1990,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1995,7 +2007,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2009,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2023,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2037,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2051,7 +2063,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2065,7 +2077,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2079,7 +2091,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2093,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2107,7 +2119,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2121,7 +2133,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2135,7 +2147,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2149,7 +2161,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2163,7 +2175,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2177,7 +2189,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2191,7 +2203,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2205,7 +2217,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2219,7 +2231,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2233,7 +2245,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2247,7 +2259,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2261,7 +2273,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2272,10 +2284,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2289,7 +2301,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2303,7 +2315,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2317,7 +2329,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2331,7 +2343,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2345,7 +2357,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2356,10 +2368,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2370,10 +2382,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2387,7 +2399,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2401,7 +2413,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2415,7 +2427,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2429,7 +2441,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2440,10 +2452,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2457,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2468,10 +2480,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2485,7 +2497,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2496,10 +2508,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2513,7 +2525,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2527,7 +2539,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2541,7 +2553,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2555,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,7 +2581,7 @@
         <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2583,7 +2595,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2597,7 +2609,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2611,7 +2623,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2625,7 +2637,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2636,10 +2648,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2653,7 +2665,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2664,10 +2676,10 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2681,7 +2693,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2695,7 +2707,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2709,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2723,7 +2735,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2737,7 +2749,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2751,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2765,7 +2777,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2779,7 +2791,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2793,7 +2805,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2804,10 +2816,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2821,7 +2833,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2835,7 +2847,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2849,7 +2861,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2863,7 +2875,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2877,7 +2889,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2891,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2905,7 +2917,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,7 +2931,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2933,7 +2945,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2947,7 +2959,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2961,7 +2973,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2975,7 +2987,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2989,7 +3001,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3003,7 +3015,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3017,7 +3029,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3031,7 +3043,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3045,7 +3057,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3059,7 +3071,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3073,7 +3085,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3087,7 +3099,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3101,7 +3113,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3112,10 +3124,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,7 +3141,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3143,7 +3155,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3157,7 +3169,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3171,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3185,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3199,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3213,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3227,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3241,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3255,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3269,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3283,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3297,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>269</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3311,7 +3323,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3325,7 +3337,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3339,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3353,7 +3365,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3367,7 +3379,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3381,7 +3393,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3395,7 +3407,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3409,7 +3421,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3423,7 +3435,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3437,7 +3449,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3451,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3465,7 +3477,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3479,7 +3491,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3493,7 +3505,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3507,7 +3519,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3521,7 +3533,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3532,10 +3544,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3546,10 +3558,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D116" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3563,7 +3575,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3574,10 +3586,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3588,10 +3600,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,7 +3617,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3619,7 +3631,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3633,7 +3645,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3647,7 +3659,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3658,10 +3670,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3675,7 +3687,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3689,7 +3701,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3703,7 +3715,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3717,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3731,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3745,7 +3757,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3759,7 +3771,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3773,7 +3785,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3787,7 +3799,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3801,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3815,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3826,10 +3838,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,7 +3855,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3857,7 +3869,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3871,7 +3883,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3885,7 +3897,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3899,7 +3911,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3913,7 +3925,7 @@
         <v>259</v>
       </c>
       <c r="D142" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3924,10 +3936,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3941,7 +3953,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3955,7 +3967,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3969,7 +3981,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3983,7 +3995,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3997,7 +4009,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4011,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,7 +4037,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4039,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4053,7 +4065,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4067,7 +4079,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4078,10 +4090,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4095,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4106,10 +4118,10 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D156" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4123,7 +4135,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4137,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4151,7 +4163,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4165,7 +4177,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4179,7 +4191,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4190,10 +4202,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4207,7 +4219,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4221,7 +4233,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4235,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4249,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4263,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4277,7 +4289,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4291,7 +4303,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4305,7 +4317,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4319,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4333,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4347,7 +4359,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4358,10 +4370,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D174" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,7 +4387,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,7 +4401,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4403,7 +4415,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4417,7 +4429,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4431,7 +4443,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4445,7 +4457,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4459,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4473,7 +4485,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4487,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4501,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4515,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4529,7 +4541,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4543,7 +4555,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4557,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4571,7 +4583,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4582,10 +4594,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D190" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4596,10 +4608,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D191" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,7 +4625,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,7 +4639,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,7 +4653,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,7 +4667,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4666,10 +4678,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4680,10 +4692,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4694,10 +4706,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D198" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,7 +4723,7 @@
         <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4725,7 +4737,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4739,7 +4751,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4753,7 +4765,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4767,7 +4779,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4781,7 +4793,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4795,7 +4807,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4809,7 +4821,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4820,10 +4832,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4837,7 +4849,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4851,7 +4863,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4865,7 +4877,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4876,10 +4888,10 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D211" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4890,10 +4902,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4907,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4921,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4935,7 +4947,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4949,7 +4961,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4963,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4977,7 +4989,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4991,7 +5003,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5005,7 +5017,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5019,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,7 +5045,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5047,7 +5059,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5061,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5075,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5089,7 +5101,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5103,7 +5115,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5117,7 +5129,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5131,7 +5143,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5145,7 +5157,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5159,7 +5171,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5173,7 +5185,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5187,7 +5199,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5201,7 +5213,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5215,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5229,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5243,7 +5255,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5257,7 +5269,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5271,7 +5283,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5285,7 +5297,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5299,7 +5311,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5313,7 +5325,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5327,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5341,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5355,7 +5367,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5369,7 +5381,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5383,7 +5395,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5397,7 +5409,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5411,7 +5423,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5422,10 +5434,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D250" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5439,7 +5451,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5453,7 +5465,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5467,7 +5479,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5481,7 +5493,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5495,7 +5507,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5509,7 +5521,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
